--- a/branches/performer-imagingstudy/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/branches/performer-imagingstudy/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:35:00+00:00</t>
+    <t>2026-10-09T08:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
